--- a/database/event/7289/event_7289_evp_summary.xlsx
+++ b/database/event/7289/event_7289_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>6.1053</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.2959</v>
       </c>
       <c r="D2" t="n">
         <v>2.045</v>
@@ -545,7 +545,7 @@
         <v>4.8742</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.8329</v>
       </c>
       <c r="D3" t="n">
         <v>1.5477</v>
@@ -591,7 +591,7 @@
         <v>4.8412</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.8205</v>
       </c>
       <c r="D4" t="n">
         <v>1.5344</v>
@@ -637,7 +637,7 @@
         <v>4.7397</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.7823</v>
       </c>
       <c r="D5" t="n">
         <v>1.4934</v>
@@ -683,7 +683,7 @@
         <v>4.3374</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.6311</v>
       </c>
       <c r="D6" t="n">
         <v>1.3309</v>
@@ -729,7 +729,7 @@
         <v>4.3329</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.6294</v>
       </c>
       <c r="D7" t="n">
         <v>1.329</v>
@@ -775,7 +775,7 @@
         <v>3.7852</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.4234</v>
       </c>
       <c r="D8" t="n">
         <v>1.1078</v>
@@ -821,7 +821,7 @@
         <v>3.77</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.4177</v>
       </c>
       <c r="D9" t="n">
         <v>1.1016</v>
@@ -867,7 +867,7 @@
         <v>3.6004</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.3539</v>
       </c>
       <c r="D10" t="n">
         <v>1.0331</v>
@@ -913,7 +913,7 @@
         <v>3.4937</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.3138</v>
       </c>
       <c r="D11" t="n">
         <v>0.99</v>
@@ -959,7 +959,7 @@
         <v>3.3373</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.255</v>
       </c>
       <c r="D12" t="n">
         <v>0.9268</v>
@@ -1005,7 +1005,7 @@
         <v>3.3142</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.2463</v>
       </c>
       <c r="D13" t="n">
         <v>0.9175</v>
@@ -1051,7 +1051,7 @@
         <v>3.2708</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="D14" t="n">
         <v>0.9</v>
@@ -1097,7 +1097,7 @@
         <v>3.2621</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.2267</v>
       </c>
       <c r="D15" t="n">
         <v>0.8965</v>
@@ -1143,7 +1143,7 @@
         <v>3.2271</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.2135</v>
       </c>
       <c r="D16" t="n">
         <v>0.8823</v>
@@ -1189,7 +1189,7 @@
         <v>3.1527</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.1856</v>
       </c>
       <c r="D17" t="n">
         <v>0.8522999999999999</v>
@@ -1235,7 +1235,7 @@
         <v>3.0372</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.1421</v>
       </c>
       <c r="D18" t="n">
         <v>0.8056</v>
@@ -1281,7 +1281,7 @@
         <v>2.9838</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.122</v>
       </c>
       <c r="D19" t="n">
         <v>0.784</v>
@@ -1327,7 +1327,7 @@
         <v>2.9265</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.1005</v>
       </c>
       <c r="D20" t="n">
         <v>0.7609</v>
@@ -1373,7 +1373,7 @@
         <v>2.7581</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.0372</v>
       </c>
       <c r="D21" t="n">
         <v>0.6928</v>
@@ -1419,7 +1419,7 @@
         <v>2.6242</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.9868</v>
       </c>
       <c r="D22" t="n">
         <v>0.6388</v>
@@ -1465,7 +1465,7 @@
         <v>2.5448</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.957</v>
       </c>
       <c r="D23" t="n">
         <v>0.6067</v>
@@ -1511,7 +1511,7 @@
         <v>2.4019</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.9032</v>
       </c>
       <c r="D24" t="n">
         <v>0.549</v>
@@ -1557,7 +1557,7 @@
         <v>2.365</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.8893</v>
       </c>
       <c r="D25" t="n">
         <v>0.534</v>
@@ -1603,7 +1603,7 @@
         <v>2.283</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.8585</v>
       </c>
       <c r="D26" t="n">
         <v>0.5009</v>
@@ -1649,7 +1649,7 @@
         <v>1.9456</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.7316</v>
       </c>
       <c r="D27" t="n">
         <v>0.3646</v>
@@ -1695,7 +1695,7 @@
         <v>1.8117</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.6813</v>
       </c>
       <c r="D28" t="n">
         <v>0.3105</v>
@@ -1741,7 +1741,7 @@
         <v>1.7749</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.6674</v>
       </c>
       <c r="D29" t="n">
         <v>0.2957</v>
@@ -1787,7 +1787,7 @@
         <v>1.7526</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.6591</v>
       </c>
       <c r="D30" t="n">
         <v>0.2866</v>
@@ -1833,7 +1833,7 @@
         <v>1.682</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.6325</v>
       </c>
       <c r="D31" t="n">
         <v>0.2581</v>
@@ -1879,7 +1879,7 @@
         <v>1.6703</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.6281</v>
       </c>
       <c r="D32" t="n">
         <v>0.2534</v>
@@ -1925,7 +1925,7 @@
         <v>1.6081</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.6047</v>
       </c>
       <c r="D33" t="n">
         <v>0.2283</v>
@@ -1971,7 +1971,7 @@
         <v>1.5132</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.569</v>
       </c>
       <c r="D34" t="n">
         <v>0.1899</v>
@@ -2017,7 +2017,7 @@
         <v>1.3258</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.4986</v>
       </c>
       <c r="D35" t="n">
         <v>0.1142</v>
@@ -2063,7 +2063,7 @@
         <v>1.1285</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.4244</v>
       </c>
       <c r="D36" t="n">
         <v>0.0345</v>
@@ -2109,7 +2109,7 @@
         <v>0.98</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.3685</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0255</v>
@@ -2155,7 +2155,7 @@
         <v>0.9651999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.363</v>
       </c>
       <c r="D38" t="n">
         <v>-0.0314</v>
@@ -2201,7 +2201,7 @@
         <v>0.78</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.2933</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1063</v>
@@ -2247,7 +2247,7 @@
         <v>0.6495</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2442</v>
       </c>
       <c r="D40" t="n">
         <v>-0.159</v>
@@ -2293,7 +2293,7 @@
         <v>0.6352</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.2389</v>
       </c>
       <c r="D41" t="n">
         <v>-0.1648</v>
@@ -2339,7 +2339,7 @@
         <v>0.4448</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.1673</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2417</v>
@@ -2385,7 +2385,7 @@
         <v>0.4091</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.1538</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2561</v>
@@ -2431,7 +2431,7 @@
         <v>0.3182</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1197</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2928</v>
@@ -2477,7 +2477,7 @@
         <v>0.3106</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.1168</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2959</v>
@@ -2523,7 +2523,7 @@
         <v>0.2963</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1114</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3017</v>
@@ -2569,7 +2569,7 @@
         <v>0.0219</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="D47" t="n">
         <v>-0.4125</v>
@@ -2615,7 +2615,7 @@
         <v>-0.018</v>
       </c>
       <c r="C48" t="n">
-        <v>-0</v>
+        <v>-0.0068</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4286</v>
@@ -2661,7 +2661,7 @@
         <v>-0.1245</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.0468</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4717</v>
@@ -2707,7 +2707,7 @@
         <v>-0.1779</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.0669</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4932</v>
@@ -2753,7 +2753,7 @@
         <v>-0.3468</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.1304</v>
       </c>
       <c r="D51" t="n">
         <v>-0.5615</v>
@@ -2799,7 +2799,7 @@
         <v>-0.3892</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.1464</v>
       </c>
       <c r="D52" t="n">
         <v>-0.5786</v>
@@ -2845,7 +2845,7 @@
         <v>-0.3925</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1476</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5799</v>
@@ -2891,7 +2891,7 @@
         <v>-0.3991</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1501</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5826</v>
@@ -2937,7 +2937,7 @@
         <v>-0.4261</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1602</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5935</v>
@@ -2983,7 +2983,7 @@
         <v>-0.4308</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.162</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5954</v>
@@ -3029,7 +3029,7 @@
         <v>-0.4769</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1793</v>
       </c>
       <c r="D57" t="n">
         <v>-0.614</v>
@@ -3075,7 +3075,7 @@
         <v>-0.5083</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.1911</v>
       </c>
       <c r="D58" t="n">
         <v>-0.6267</v>
@@ -3121,7 +3121,7 @@
         <v>-0.5215</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.1961</v>
       </c>
       <c r="D59" t="n">
         <v>-0.632</v>
@@ -3167,7 +3167,7 @@
         <v>-0.579</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2177</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6553</v>
@@ -3213,7 +3213,7 @@
         <v>-0.678</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.255</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6953</v>
@@ -3259,7 +3259,7 @@
         <v>-0.7528</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.2831</v>
       </c>
       <c r="D62" t="n">
         <v>-0.7255</v>
@@ -3305,7 +3305,7 @@
         <v>-0.7923</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.2979</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7413999999999999</v>
@@ -3351,7 +3351,7 @@
         <v>-0.8338</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.3135</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7582</v>
@@ -3397,7 +3397,7 @@
         <v>-0.8447</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.3176</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7625999999999999</v>
@@ -3443,7 +3443,7 @@
         <v>-1.0126</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.3808</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8304</v>
@@ -3489,7 +3489,7 @@
         <v>-1.0344</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.389</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8391999999999999</v>
@@ -3535,7 +3535,7 @@
         <v>-1.2099</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.455</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9101</v>
@@ -3581,7 +3581,7 @@
         <v>-1.2515</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.4706</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9268999999999999</v>
@@ -3627,7 +3627,7 @@
         <v>-1.2824</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.4822</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9394</v>
@@ -3673,7 +3673,7 @@
         <v>-1.3259</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.4986</v>
       </c>
       <c r="D71" t="n">
         <v>-0.957</v>
@@ -3719,7 +3719,7 @@
         <v>-1.3642</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.513</v>
       </c>
       <c r="D72" t="n">
         <v>-0.9725</v>
@@ -3765,7 +3765,7 @@
         <v>-1.4513</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.5458</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0077</v>
@@ -3811,7 +3811,7 @@
         <v>-1.5237</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.573</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0369</v>
@@ -3857,7 +3857,7 @@
         <v>-1.5565</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.5853</v>
       </c>
       <c r="D75" t="n">
         <v>-1.0502</v>
@@ -3903,7 +3903,7 @@
         <v>-1.7131</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.6442</v>
       </c>
       <c r="D76" t="n">
         <v>-1.1134</v>
@@ -3949,7 +3949,7 @@
         <v>-1.9018</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1896</v>
@@ -3995,7 +3995,7 @@
         <v>-1.91</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="D78" t="n">
         <v>-1.193</v>
@@ -4041,7 +4041,7 @@
         <v>-2</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-0.7521</v>
       </c>
       <c r="D79" t="n">
         <v>-1.2293</v>
@@ -4087,7 +4087,7 @@
         <v>-2.5866</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-0.9727</v>
       </c>
       <c r="D80" t="n">
         <v>-1.4663</v>
@@ -4133,7 +4133,7 @@
         <v>-4.3179</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.6237</v>
       </c>
       <c r="D81" t="n">
         <v>-2.1657</v>

--- a/database/event/7289/event_7289_evp_summary.xlsx
+++ b/database/event/7289/event_7289_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1053</v>
+        <v>5.9352</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2959</v>
+        <v>2.2319</v>
       </c>
       <c r="D2" t="n">
-        <v>2.045</v>
+        <v>1.9207</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1053</v>
+        <v>5.9352</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1053</v>
+        <v>5.9352</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.27</v>
+        <v>7.0033</v>
       </c>
       <c r="I2" t="n">
         <v>7.6155</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.8742</v>
+        <v>4.7493</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8329</v>
+        <v>1.7859</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5477</v>
+        <v>1.4482</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8742</v>
+        <v>4.7493</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8742</v>
+        <v>4.7493</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3397</v>
+        <v>5.1438</v>
       </c>
       <c r="I3" t="n">
         <v>5.5935</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8412</v>
+        <v>4.7175</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8205</v>
+        <v>1.774</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5344</v>
+        <v>1.4355</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8412</v>
+        <v>4.7175</v>
       </c>
       <c r="F4" t="n">
-        <v>4.8412</v>
+        <v>4.7175</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2879</v>
+        <v>5.0939</v>
       </c>
       <c r="I4" t="n">
         <v>5.5393</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7397</v>
+        <v>4.6552</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7823</v>
+        <v>1.7506</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4934</v>
+        <v>1.4107</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7397</v>
+        <v>4.6552</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7397</v>
+        <v>4.6552</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1287</v>
+        <v>4.9963</v>
       </c>
       <c r="I5" t="n">
         <v>5.2982</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3374</v>
+        <v>4.2425</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6311</v>
+        <v>1.5954</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3309</v>
+        <v>1.2463</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3374</v>
+        <v>4.2425</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3374</v>
+        <v>4.2425</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4979</v>
+        <v>4.3491</v>
       </c>
       <c r="I6" t="n">
         <v>4.6899</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3329</v>
+        <v>4.2381</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6294</v>
+        <v>1.5937</v>
       </c>
       <c r="D7" t="n">
-        <v>1.329</v>
+        <v>1.2445</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3329</v>
+        <v>4.2381</v>
       </c>
       <c r="F7" t="n">
-        <v>4.3329</v>
+        <v>4.2381</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4909</v>
+        <v>4.3423</v>
       </c>
       <c r="I7" t="n">
         <v>4.6826</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7852</v>
+        <v>3.729</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4234</v>
+        <v>1.4023</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1078</v>
+        <v>1.0417</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7852</v>
+        <v>3.729</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7852</v>
+        <v>3.729</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7852</v>
+        <v>3.729</v>
       </c>
       <c r="I8" t="n">
         <v>3.8562</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.77</v>
+        <v>3.7002</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4177</v>
+        <v>1.3914</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1016</v>
+        <v>1.0302</v>
       </c>
       <c r="E9" t="n">
-        <v>3.77</v>
+        <v>3.7002</v>
       </c>
       <c r="F9" t="n">
-        <v>3.77</v>
+        <v>3.7002</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.77</v>
+        <v>3.7002</v>
       </c>
       <c r="I9" t="n">
         <v>3.8585</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6004</v>
+        <v>3.5469</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3539</v>
+        <v>1.3338</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0331</v>
+        <v>0.9692</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6004</v>
+        <v>3.5469</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6004</v>
+        <v>3.5469</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6004</v>
+        <v>3.5469</v>
       </c>
       <c r="I10" t="n">
         <v>3.6679</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4937</v>
+        <v>3.429</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3138</v>
+        <v>1.2895</v>
       </c>
       <c r="D11" t="n">
-        <v>0.99</v>
+        <v>0.9222</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4937</v>
+        <v>3.429</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4937</v>
+        <v>3.429</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4937</v>
+        <v>3.429</v>
       </c>
       <c r="I11" t="n">
         <v>3.5757</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3373</v>
+        <v>3.2755</v>
       </c>
       <c r="C12" t="n">
-        <v>1.255</v>
+        <v>1.2317</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9268</v>
+        <v>0.861</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3373</v>
+        <v>3.2755</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3373</v>
+        <v>3.2755</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3373</v>
+        <v>3.2755</v>
       </c>
       <c r="I12" t="n">
         <v>3.4156</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3142</v>
+        <v>3.2528</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2463</v>
+        <v>1.2232</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9175</v>
+        <v>0.852</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3142</v>
+        <v>3.2528</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3142</v>
+        <v>3.2528</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3142</v>
+        <v>3.2528</v>
       </c>
       <c r="I13" t="n">
         <v>3.392</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2708</v>
+        <v>3.2222</v>
       </c>
       <c r="C14" t="n">
-        <v>1.23</v>
+        <v>1.2117</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9</v>
+        <v>0.8398</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2708</v>
+        <v>3.2222</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2708</v>
+        <v>3.2222</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2708</v>
+        <v>3.2222</v>
       </c>
       <c r="I14" t="n">
         <v>3.3321</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.2621</v>
+        <v>3.2137</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2267</v>
+        <v>1.2085</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8965</v>
+        <v>0.8364</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2621</v>
+        <v>3.2137</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2621</v>
+        <v>3.2137</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2621</v>
+        <v>3.2137</v>
       </c>
       <c r="I15" t="n">
         <v>3.3233</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.2271</v>
+        <v>3.1437</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2135</v>
+        <v>1.1822</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8823</v>
+        <v>0.8085</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2271</v>
+        <v>3.1437</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2271</v>
+        <v>3.1437</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2271</v>
+        <v>3.1437</v>
       </c>
       <c r="I16" t="n">
         <v>3.3337</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.1527</v>
+        <v>3.0944</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1856</v>
+        <v>1.1636</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.7889</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1527</v>
+        <v>3.0944</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1527</v>
+        <v>3.0944</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1527</v>
+        <v>3.0944</v>
       </c>
       <c r="I17" t="n">
         <v>3.2268</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.0372</v>
+        <v>2.9588</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1421</v>
+        <v>1.1126</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8056</v>
+        <v>0.7349</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0372</v>
+        <v>2.9588</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0372</v>
+        <v>2.9588</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0372</v>
+        <v>2.9588</v>
       </c>
       <c r="I18" t="n">
         <v>3.1376</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.9838</v>
+        <v>2.9067</v>
       </c>
       <c r="C19" t="n">
-        <v>1.122</v>
+        <v>1.093</v>
       </c>
       <c r="D19" t="n">
-        <v>0.784</v>
+        <v>0.7141</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9838</v>
+        <v>2.9067</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9838</v>
+        <v>2.9067</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9838</v>
+        <v>2.9067</v>
       </c>
       <c r="I19" t="n">
         <v>3.0823</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9265</v>
+        <v>2.851</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1005</v>
+        <v>1.0721</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7609</v>
+        <v>0.6919</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9265</v>
+        <v>2.851</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9265</v>
+        <v>2.851</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9265</v>
+        <v>2.851</v>
       </c>
       <c r="I20" t="n">
         <v>3.0232</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7581</v>
+        <v>2.6869</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0372</v>
+        <v>1.0104</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6928</v>
+        <v>0.6266</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7581</v>
+        <v>2.6869</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7581</v>
+        <v>2.6869</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7581</v>
+        <v>2.6869</v>
       </c>
       <c r="I21" t="n">
         <v>2.8493</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6242</v>
+        <v>2.5853</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9868</v>
+        <v>0.9722</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6388</v>
+        <v>0.5861</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6242</v>
+        <v>2.5853</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6242</v>
+        <v>2.5853</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6242</v>
+        <v>2.5853</v>
       </c>
       <c r="I22" t="n">
         <v>2.6734</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.5448</v>
+        <v>2.4791</v>
       </c>
       <c r="C23" t="n">
-        <v>0.957</v>
+        <v>0.9323</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6067</v>
+        <v>0.5438</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5448</v>
+        <v>2.4791</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5448</v>
+        <v>2.4791</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5448</v>
+        <v>2.4791</v>
       </c>
       <c r="I23" t="n">
         <v>2.6289</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.4019</v>
+        <v>2.3574</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9032</v>
+        <v>0.8865</v>
       </c>
       <c r="D24" t="n">
-        <v>0.549</v>
+        <v>0.4953</v>
       </c>
       <c r="E24" t="n">
-        <v>2.4019</v>
+        <v>2.3574</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4019</v>
+        <v>2.3574</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.4019</v>
+        <v>2.3574</v>
       </c>
       <c r="I24" t="n">
         <v>2.4583</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.365</v>
+        <v>2.3474</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8893</v>
+        <v>0.8827</v>
       </c>
       <c r="D25" t="n">
-        <v>0.534</v>
+        <v>0.4913</v>
       </c>
       <c r="E25" t="n">
-        <v>2.365</v>
+        <v>2.3474</v>
       </c>
       <c r="F25" t="n">
-        <v>2.365</v>
+        <v>2.3474</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.365</v>
+        <v>2.3474</v>
       </c>
       <c r="I25" t="n">
         <v>2.387</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.283</v>
+        <v>2.2491</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8585</v>
+        <v>0.8458</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5009</v>
+        <v>0.4521</v>
       </c>
       <c r="E26" t="n">
-        <v>2.283</v>
+        <v>2.2491</v>
       </c>
       <c r="F26" t="n">
-        <v>2.283</v>
+        <v>2.2491</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.283</v>
+        <v>2.2491</v>
       </c>
       <c r="I26" t="n">
         <v>2.3258</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9456</v>
+        <v>1.9312</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7316</v>
+        <v>0.7262</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3646</v>
+        <v>0.3255</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9456</v>
+        <v>1.9312</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9456</v>
+        <v>1.9312</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9456</v>
+        <v>1.9312</v>
       </c>
       <c r="I27" t="n">
         <v>1.9638</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.8117</v>
+        <v>1.7518</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6813</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3105</v>
+        <v>0.254</v>
       </c>
       <c r="E28" t="n">
-        <v>1.8117</v>
+        <v>1.7518</v>
       </c>
       <c r="F28" t="n">
-        <v>1.8117</v>
+        <v>1.7518</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.8117</v>
+        <v>1.7518</v>
       </c>
       <c r="I28" t="n">
         <v>1.889</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.7749</v>
+        <v>1.7202</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6674</v>
+        <v>0.6469</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2957</v>
+        <v>0.2414</v>
       </c>
       <c r="E29" t="n">
-        <v>1.7749</v>
+        <v>1.7202</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7749</v>
+        <v>1.7202</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7749</v>
+        <v>1.7202</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8506</v>
+        <v>1.7938</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>379</v>
+        <v>207</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.8506</v>
+        <v>1.7938</v>
       </c>
       <c r="N29" t="n">
-        <v>379</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.7526</v>
+        <v>1.7162</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6591</v>
+        <v>0.6454</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2866</v>
+        <v>0.2398</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7526</v>
+        <v>1.7162</v>
       </c>
       <c r="F30" t="n">
-        <v>1.7526</v>
+        <v>1.7162</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.7526</v>
+        <v>1.7162</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7938</v>
+        <v>1.8506</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>207</v>
+        <v>379</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.7938</v>
+        <v>1.8506</v>
       </c>
       <c r="N30" t="n">
-        <v>207</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31">
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.682</v>
+        <v>1.6571</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6325</v>
+        <v>0.6231</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2581</v>
+        <v>0.2163</v>
       </c>
       <c r="E31" t="n">
-        <v>1.682</v>
+        <v>1.6571</v>
       </c>
       <c r="F31" t="n">
-        <v>1.682</v>
+        <v>1.6571</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.682</v>
+        <v>1.6571</v>
       </c>
       <c r="I31" t="n">
         <v>1.7136</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.6703</v>
+        <v>1.6516</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6281</v>
+        <v>0.6211</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2534</v>
+        <v>0.2141</v>
       </c>
       <c r="E32" t="n">
-        <v>1.6703</v>
+        <v>1.6516</v>
       </c>
       <c r="F32" t="n">
-        <v>1.6703</v>
+        <v>1.6516</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.6703</v>
+        <v>1.6516</v>
       </c>
       <c r="I32" t="n">
         <v>1.6937</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.6081</v>
+        <v>1.5665</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6047</v>
+        <v>0.5891</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2283</v>
+        <v>0.1802</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6081</v>
+        <v>1.5665</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6081</v>
+        <v>1.5665</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6081</v>
+        <v>1.5665</v>
       </c>
       <c r="I33" t="n">
         <v>1.6612</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.5132</v>
+        <v>1.4851</v>
       </c>
       <c r="C34" t="n">
-        <v>0.569</v>
+        <v>0.5585</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1899</v>
+        <v>0.1478</v>
       </c>
       <c r="E34" t="n">
-        <v>1.5132</v>
+        <v>1.4851</v>
       </c>
       <c r="F34" t="n">
-        <v>1.5132</v>
+        <v>1.4851</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5132</v>
+        <v>1.4851</v>
       </c>
       <c r="I34" t="n">
         <v>1.5487</v>
@@ -2020,7 +2020,7 @@
         <v>0.4986</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1142</v>
+        <v>0.0843</v>
       </c>
       <c r="E35" t="n">
         <v>1.3258</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.1285</v>
+        <v>1.1243</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4244</v>
+        <v>0.4228</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0345</v>
+        <v>0.004</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1285</v>
+        <v>1.1243</v>
       </c>
       <c r="F36" t="n">
-        <v>1.1285</v>
+        <v>1.1243</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1285</v>
+        <v>1.1243</v>
       </c>
       <c r="I36" t="n">
         <v>1.1338</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.98</v>
+        <v>0.969</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3685</v>
+        <v>0.3644</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0255</v>
+        <v>-0.0579</v>
       </c>
       <c r="E37" t="n">
-        <v>0.98</v>
+        <v>0.969</v>
       </c>
       <c r="F37" t="n">
-        <v>0.98</v>
+        <v>0.969</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.98</v>
+        <v>0.969</v>
       </c>
       <c r="I37" t="n">
         <v>0.9937</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9616</v>
       </c>
       <c r="C38" t="n">
-        <v>0.363</v>
+        <v>0.3616</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0314</v>
+        <v>-0.0608</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9616</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9616</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9616</v>
       </c>
       <c r="I38" t="n">
         <v>0.9697</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.78</v>
+        <v>0.7713</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2933</v>
+        <v>0.29</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1063</v>
+        <v>-0.1366</v>
       </c>
       <c r="E39" t="n">
-        <v>0.78</v>
+        <v>0.7713</v>
       </c>
       <c r="F39" t="n">
-        <v>0.78</v>
+        <v>0.7713</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.78</v>
+        <v>0.7713</v>
       </c>
       <c r="I39" t="n">
         <v>0.7909</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6495</v>
+        <v>0.6422</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2442</v>
+        <v>0.2415</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.159</v>
+        <v>-0.1881</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6495</v>
+        <v>0.6422</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6495</v>
+        <v>0.6422</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6495</v>
+        <v>0.6422</v>
       </c>
       <c r="I40" t="n">
         <v>0.6586</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6352</v>
+        <v>0.6281</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2389</v>
+        <v>0.2362</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1648</v>
+        <v>-0.1937</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6352</v>
+        <v>0.6281</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6352</v>
+        <v>0.6281</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6352</v>
+        <v>0.6281</v>
       </c>
       <c r="I41" t="n">
         <v>0.6441</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4448</v>
+        <v>0.4414</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1673</v>
+        <v>0.166</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2417</v>
+        <v>-0.2681</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4448</v>
+        <v>0.4414</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4448</v>
+        <v>0.4414</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4448</v>
+        <v>0.4414</v>
       </c>
       <c r="I42" t="n">
         <v>0.4489</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4091</v>
+        <v>0.4076</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1538</v>
+        <v>0.1533</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2561</v>
+        <v>-0.2815</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4091</v>
+        <v>0.4076</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4091</v>
+        <v>0.4076</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4091</v>
+        <v>0.4076</v>
       </c>
       <c r="I43" t="n">
         <v>0.411</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3182</v>
+        <v>0.3135</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1197</v>
+        <v>0.1179</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2928</v>
+        <v>-0.319</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3182</v>
+        <v>0.3135</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3182</v>
+        <v>0.3135</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3182</v>
+        <v>0.3135</v>
       </c>
       <c r="I44" t="n">
         <v>0.3242</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3106</v>
+        <v>0.306</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1168</v>
+        <v>0.1151</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2959</v>
+        <v>-0.322</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3106</v>
+        <v>0.306</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3106</v>
+        <v>0.306</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3106</v>
+        <v>0.306</v>
       </c>
       <c r="I45" t="n">
         <v>0.3164</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2963</v>
+        <v>0.2919</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1114</v>
+        <v>0.1098</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3017</v>
+        <v>-0.3276</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2963</v>
+        <v>0.2919</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2963</v>
+        <v>0.2919</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2963</v>
+        <v>0.2919</v>
       </c>
       <c r="I46" t="n">
         <v>0.3019</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0219</v>
+        <v>0.0213</v>
       </c>
       <c r="C47" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4125</v>
+        <v>-0.4354</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0219</v>
+        <v>0.0213</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0219</v>
+        <v>0.0213</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0219</v>
+        <v>0.0213</v>
       </c>
       <c r="I47" t="n">
         <v>0.0226</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.018</v>
+        <v>-0.0178</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0068</v>
+        <v>-0.0067</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4286</v>
+        <v>-0.451</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.018</v>
+        <v>-0.0178</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.018</v>
+        <v>-0.0178</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.018</v>
+        <v>-0.0178</v>
       </c>
       <c r="I48" t="n">
         <v>-0.0183</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1245</v>
+        <v>-0.1204</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0468</v>
+        <v>-0.0453</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4717</v>
+        <v>-0.4919</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1245</v>
+        <v>-0.1204</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1245</v>
+        <v>-0.1204</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1245</v>
+        <v>-0.1204</v>
       </c>
       <c r="I49" t="n">
         <v>-0.1298</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1779</v>
+        <v>-0.1766</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0669</v>
+        <v>-0.0664</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4932</v>
+        <v>-0.5143</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1779</v>
+        <v>-0.1766</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1779</v>
+        <v>-0.1766</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1779</v>
+        <v>-0.1766</v>
       </c>
       <c r="I50" t="n">
         <v>-0.1796</v>
@@ -2756,7 +2756,7 @@
         <v>-0.1304</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5615</v>
+        <v>-0.5821</v>
       </c>
       <c r="E51" t="n">
         <v>-0.3468</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3892</v>
+        <v>-0.3877</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1464</v>
+        <v>-0.1458</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5786</v>
+        <v>-0.5984</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.3892</v>
+        <v>-0.3877</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3892</v>
+        <v>-0.3877</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3892</v>
+        <v>-0.3877</v>
       </c>
       <c r="I52" t="n">
         <v>-0.391</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3925</v>
+        <v>-0.391</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1476</v>
+        <v>-0.147</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5799</v>
+        <v>-0.5997</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3925</v>
+        <v>-0.391</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3925</v>
+        <v>-0.391</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3925</v>
+        <v>-0.391</v>
       </c>
       <c r="I53" t="n">
         <v>-0.3943</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3991</v>
+        <v>-0.3947</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1501</v>
+        <v>-0.1484</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5826</v>
+        <v>-0.6012</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3991</v>
+        <v>-0.3947</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3991</v>
+        <v>-0.3947</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3991</v>
+        <v>-0.3947</v>
       </c>
       <c r="I54" t="n">
         <v>-0.4047</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4261</v>
+        <v>-0.4245</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1602</v>
+        <v>-0.1596</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5935</v>
+        <v>-0.613</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4261</v>
+        <v>-0.4245</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4261</v>
+        <v>-0.4245</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4261</v>
+        <v>-0.4245</v>
       </c>
       <c r="I55" t="n">
         <v>-0.4281</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4308</v>
+        <v>-0.426</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.162</v>
+        <v>-0.1602</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5954</v>
+        <v>-0.6136</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4308</v>
+        <v>-0.426</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4308</v>
+        <v>-0.426</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4308</v>
+        <v>-0.426</v>
       </c>
       <c r="I56" t="n">
         <v>-0.4368</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4769</v>
+        <v>-0.4698</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1793</v>
+        <v>-0.1767</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.614</v>
+        <v>-0.6311</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4769</v>
+        <v>-0.4698</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.4769</v>
+        <v>-0.4698</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.4769</v>
+        <v>-0.4698</v>
       </c>
       <c r="I57" t="n">
         <v>-0.4858</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5083</v>
+        <v>-0.5026</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1911</v>
+        <v>-0.189</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6267</v>
+        <v>-0.6441</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5083</v>
+        <v>-0.5026</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5083</v>
+        <v>-0.5026</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5083</v>
+        <v>-0.5026</v>
       </c>
       <c r="I58" t="n">
         <v>-0.5154</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5215</v>
+        <v>-0.508</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1961</v>
+        <v>-0.191</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.632</v>
+        <v>-0.6463</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5215</v>
+        <v>-0.508</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5215</v>
+        <v>-0.508</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5215</v>
+        <v>-0.508</v>
       </c>
       <c r="I59" t="n">
         <v>-0.5387</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.579</v>
+        <v>-0.5725</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2177</v>
+        <v>-0.2153</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6553</v>
+        <v>-0.672</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.579</v>
+        <v>-0.5725</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.579</v>
+        <v>-0.5725</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.579</v>
+        <v>-0.5725</v>
       </c>
       <c r="I60" t="n">
         <v>-0.5871</v>
@@ -3216,7 +3216,7 @@
         <v>-0.255</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6953</v>
+        <v>-0.714</v>
       </c>
       <c r="E61" t="n">
         <v>-0.678</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2831</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7255</v>
+        <v>-0.7438</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7528</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7923</v>
+        <v>-0.7894</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2979</v>
+        <v>-0.2968</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.7584</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7923</v>
+        <v>-0.7894</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7923</v>
+        <v>-0.7894</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7923</v>
+        <v>-0.7894</v>
       </c>
       <c r="I63" t="n">
         <v>-0.796</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.8338</v>
+        <v>-0.8032</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3135</v>
+        <v>-0.302</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7582</v>
+        <v>-0.7639</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.8338</v>
+        <v>-0.8032</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.8338</v>
+        <v>-0.8032</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.8338</v>
+        <v>-0.8032</v>
       </c>
       <c r="I64" t="n">
         <v>-0.8734</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8447</v>
+        <v>-0.8415</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3176</v>
+        <v>-0.3164</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-0.7792</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8447</v>
+        <v>-0.8415</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8447</v>
+        <v>-0.8415</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8447</v>
+        <v>-0.8415</v>
       </c>
       <c r="I65" t="n">
         <v>-0.8486</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0126</v>
+        <v>-1.0088</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3808</v>
+        <v>-0.3794</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8304</v>
+        <v>-0.8458</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.0126</v>
+        <v>-1.0088</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.0126</v>
+        <v>-1.0088</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.0126</v>
+        <v>-1.0088</v>
       </c>
       <c r="I66" t="n">
         <v>-1.0173</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.0344</v>
+        <v>-1.0305</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.389</v>
+        <v>-0.3875</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.8545</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.0344</v>
+        <v>-1.0305</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.0344</v>
+        <v>-1.0305</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.0344</v>
+        <v>-1.0305</v>
       </c>
       <c r="I67" t="n">
         <v>-1.0392</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.2099</v>
+        <v>-1.2054</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.455</v>
+        <v>-0.4533</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9101</v>
+        <v>-0.9241</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2099</v>
+        <v>-1.2054</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.2099</v>
+        <v>-1.2054</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.2099</v>
+        <v>-1.2054</v>
       </c>
       <c r="I68" t="n">
         <v>-1.2155</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.2515</v>
+        <v>-1.2422</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4706</v>
+        <v>-0.4671</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.9388</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2515</v>
+        <v>-1.2422</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.2515</v>
+        <v>-1.2422</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.2515</v>
+        <v>-1.2422</v>
       </c>
       <c r="I69" t="n">
         <v>-1.2632</v>
@@ -3620,93 +3620,93 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.2824</v>
+        <v>-1.2772</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4822</v>
+        <v>-0.4803</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9394</v>
+        <v>-0.9527</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2824</v>
+        <v>-1.2772</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.2824</v>
+        <v>-1.2772</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.2824</v>
+        <v>-1.2772</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2884</v>
+        <v>-1.3889</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.2884</v>
+        <v>-1.3889</v>
       </c>
       <c r="N70" t="n">
-        <v>97</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.3259</v>
+        <v>-1.2776</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4986</v>
+        <v>-0.4804</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.957</v>
+        <v>-0.9529</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.3259</v>
+        <v>-1.2776</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.3259</v>
+        <v>-1.2776</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.3259</v>
+        <v>-1.2776</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.3889</v>
+        <v>-1.2884</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.3889</v>
+        <v>-1.2884</v>
       </c>
       <c r="N71" t="n">
-        <v>258</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72">
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3642</v>
+        <v>-1.344</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.513</v>
+        <v>-0.5054</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9725</v>
+        <v>-0.9794</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3642</v>
+        <v>-1.344</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.3642</v>
+        <v>-1.344</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.3642</v>
+        <v>-1.344</v>
       </c>
       <c r="I72" t="n">
         <v>-1.3898</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.4513</v>
+        <v>-1.4244</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5458</v>
+        <v>-0.5356</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0077</v>
+        <v>-1.0114</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.4513</v>
+        <v>-1.4244</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.4513</v>
+        <v>-1.4244</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.4513</v>
+        <v>-1.4244</v>
       </c>
       <c r="I73" t="n">
         <v>-1.4854</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.5237</v>
+        <v>-1.518</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.573</v>
+        <v>-0.5708</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0369</v>
+        <v>-1.0487</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.5237</v>
+        <v>-1.518</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.5237</v>
+        <v>-1.518</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.5237</v>
+        <v>-1.518</v>
       </c>
       <c r="I74" t="n">
         <v>-1.5308</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.5565</v>
+        <v>-1.5506</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5853</v>
+        <v>-0.5831</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0502</v>
+        <v>-1.0617</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.5565</v>
+        <v>-1.5506</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.5565</v>
+        <v>-1.5506</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.5565</v>
+        <v>-1.5506</v>
       </c>
       <c r="I75" t="n">
         <v>-1.5637</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.7131</v>
+        <v>-1.6877</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6442</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1134</v>
+        <v>-1.1163</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.7131</v>
+        <v>-1.6877</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.7131</v>
+        <v>-1.6877</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.7131</v>
+        <v>-1.6877</v>
       </c>
       <c r="I76" t="n">
         <v>-1.7452</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cJ dA K1nG</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.9018</v>
+        <v>-1.8816</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.7076</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1896</v>
+        <v>-1.1935</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.9018</v>
+        <v>-1.8816</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.9018</v>
+        <v>-1.8816</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.9018</v>
+        <v>-1.8816</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.9107</v>
+        <v>-1.9458</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>97</v>
+        <v>197</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.9107</v>
+        <v>-1.9458</v>
       </c>
       <c r="N77" t="n">
-        <v>97</v>
+        <v>197</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>cJ dA K1nG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.91</v>
+        <v>-1.8948</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.7125</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.193</v>
+        <v>-1.1988</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.91</v>
+        <v>-1.8948</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.91</v>
+        <v>-1.8948</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.91</v>
+        <v>-1.8948</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.9458</v>
+        <v>-1.9107</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.9458</v>
+        <v>-1.9107</v>
       </c>
       <c r="N78" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79">
@@ -4044,7 +4044,7 @@
         <v>-0.7521</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E79" t="n">
         <v>-2</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.5866</v>
+        <v>-2.5482</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.9727</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4663</v>
+        <v>-1.4591</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.5866</v>
+        <v>-2.5482</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.5866</v>
+        <v>-2.5482</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.5866</v>
+        <v>-2.5482</v>
       </c>
       <c r="I80" t="n">
         <v>-2.6351</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.3179</v>
+        <v>-4.2379</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.6237</v>
+        <v>-1.5936</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.1657</v>
+        <v>-2.1323</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.3179</v>
+        <v>-4.2379</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.3179</v>
+        <v>-4.2379</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.3179</v>
+        <v>-4.2379</v>
       </c>
       <c r="I81" t="n">
         <v>-4.4193</v>

--- a/database/event/7289/event_7289_evp_summary.xlsx
+++ b/database/event/7289/event_7289_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.6568</v>
+        <v>4.8594</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7512</v>
+        <v>1.8273</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4957</v>
+        <v>1.5568</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6568</v>
+        <v>4.8594</v>
       </c>
       <c r="F2" t="n">
         <v>4.6568</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.9788</v>
+        <v>4.1479</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4962</v>
+        <v>1.5598</v>
       </c>
       <c r="D3" t="n">
-        <v>1.187</v>
+        <v>1.239</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9788</v>
+        <v>4.1479</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9788</v>
+        <v>3.7901</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9834</v>
+        <v>5.5704</v>
       </c>
       <c r="I3" t="n">
-        <v>7.7169</v>
+        <v>6.6563</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7.7169</v>
+        <v>6.6563</v>
       </c>
       <c r="N3" t="n">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.79</v>
+        <v>4.1317</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4252</v>
+        <v>1.5537</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1011</v>
+        <v>1.2317</v>
       </c>
       <c r="E4" t="n">
-        <v>3.79</v>
+        <v>4.1317</v>
       </c>
       <c r="F4" t="n">
-        <v>3.79</v>
+        <v>3.9788</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5701</v>
+        <v>5.9834</v>
       </c>
       <c r="I4" t="n">
-        <v>6.656</v>
+        <v>7.7169</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6.656</v>
+        <v>7.7169</v>
       </c>
       <c r="N4" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.68</v>
+        <v>4.0233</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3838</v>
+        <v>1.5129</v>
       </c>
       <c r="D5" t="n">
-        <v>1.051</v>
+        <v>1.1833</v>
       </c>
       <c r="E5" t="n">
-        <v>3.68</v>
+        <v>4.0233</v>
       </c>
       <c r="F5" t="n">
         <v>3.68</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6537</v>
+        <v>3.8384</v>
       </c>
       <c r="C6" t="n">
-        <v>1.374</v>
+        <v>1.4434</v>
       </c>
       <c r="D6" t="n">
-        <v>1.039</v>
+        <v>1.1007</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6537</v>
+        <v>3.8384</v>
       </c>
       <c r="F6" t="n">
         <v>3.6537</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5889</v>
+        <v>3.8106</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3496</v>
+        <v>1.433</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0095</v>
+        <v>1.0883</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5889</v>
+        <v>3.8106</v>
       </c>
       <c r="F7" t="n">
         <v>3.5889</v>
@@ -768,507 +768,507 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3906</v>
+        <v>3.6824</v>
       </c>
       <c r="C8" t="n">
-        <v>1.275</v>
+        <v>1.3847</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9193</v>
+        <v>1.031</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3906</v>
+        <v>3.6824</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3906</v>
+        <v>3.1401</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.696</v>
+        <v>4.1477</v>
       </c>
       <c r="I8" t="n">
-        <v>6.0565</v>
+        <v>4.592</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6.0565</v>
+        <v>4.592</v>
       </c>
       <c r="N8" t="n">
-        <v>258</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3663</v>
+        <v>3.6217</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2659</v>
+        <v>1.3619</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9082</v>
+        <v>1.0039</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3663</v>
+        <v>3.6217</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3663</v>
+        <v>3.2715</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6429</v>
+        <v>4.4354</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2728</v>
+        <v>4.9106</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.2728</v>
+        <v>4.9106</v>
       </c>
       <c r="N9" t="n">
-        <v>207</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2715</v>
+        <v>3.5809</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2302</v>
+        <v>1.3466</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8651</v>
+        <v>0.9857</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2715</v>
+        <v>3.5809</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2715</v>
+        <v>3.3906</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4354</v>
+        <v>4.696</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9106</v>
+        <v>6.0565</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>137</v>
+        <v>258</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.9106</v>
+        <v>6.0565</v>
       </c>
       <c r="N10" t="n">
-        <v>137</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2582</v>
+        <v>3.5559</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2252</v>
+        <v>1.3372</v>
       </c>
       <c r="D11" t="n">
-        <v>0.859</v>
+        <v>0.9745</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2582</v>
+        <v>3.5559</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2582</v>
+        <v>3.3663</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4064</v>
+        <v>4.6429</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8784</v>
+        <v>5.2728</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8784</v>
+        <v>5.2728</v>
       </c>
       <c r="N11" t="n">
-        <v>170</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2011</v>
+        <v>3.4529</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2038</v>
+        <v>1.2984</v>
       </c>
       <c r="D12" t="n">
-        <v>0.833</v>
+        <v>0.9285</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2011</v>
+        <v>3.4529</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2011</v>
+        <v>3.2582</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2813</v>
+        <v>4.4064</v>
       </c>
       <c r="I12" t="n">
-        <v>5.383</v>
+        <v>4.8784</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>379</v>
+        <v>170</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.383</v>
+        <v>4.8784</v>
       </c>
       <c r="N12" t="n">
-        <v>379</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1401</v>
+        <v>3.3936</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1808</v>
+        <v>1.2761</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8052</v>
+        <v>0.902</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1401</v>
+        <v>3.3936</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1401</v>
+        <v>2.9718</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1477</v>
+        <v>3.7793</v>
       </c>
       <c r="I13" t="n">
-        <v>4.592</v>
+        <v>4.1842</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.592</v>
+        <v>4.1842</v>
       </c>
       <c r="N13" t="n">
-        <v>197</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1004</v>
+        <v>3.2963</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1659</v>
+        <v>1.2396</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7872</v>
+        <v>0.8586</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1004</v>
+        <v>3.2963</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1004</v>
+        <v>3.2011</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0608</v>
+        <v>4.2813</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8524</v>
+        <v>5.383</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>246</v>
+        <v>379</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.8524</v>
+        <v>5.383</v>
       </c>
       <c r="N14" t="n">
-        <v>246</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0485</v>
+        <v>3.2196</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1464</v>
+        <v>1.2107</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7635</v>
+        <v>0.8243</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0485</v>
+        <v>3.2196</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0485</v>
+        <v>3.1005</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9472</v>
+        <v>4.0611</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4827</v>
+        <v>4.8528</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4827</v>
+        <v>4.8528</v>
       </c>
       <c r="N15" t="n">
-        <v>207</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>story</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9718</v>
+        <v>3.0477</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1175</v>
+        <v>1.1461</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7286</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9718</v>
+        <v>3.0477</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9718</v>
+        <v>2.8596</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7793</v>
+        <v>3.5339</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1842</v>
+        <v>3.7184</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1842</v>
+        <v>3.7184</v>
       </c>
       <c r="N16" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9151</v>
+        <v>3.0418</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0962</v>
+        <v>1.1439</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7028</v>
+        <v>0.7449</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9151</v>
+        <v>3.0418</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9151</v>
+        <v>3.0485</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6554</v>
+        <v>3.9472</v>
       </c>
       <c r="I17" t="n">
-        <v>4.368</v>
+        <v>4.4827</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>246</v>
+        <v>207</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.368</v>
+        <v>4.4827</v>
       </c>
       <c r="N17" t="n">
-        <v>246</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.8699</v>
+        <v>2.9891</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0792</v>
+        <v>1.124</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6822</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8699</v>
+        <v>2.9891</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8699</v>
+        <v>2.7651</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5564</v>
+        <v>3.327</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7421</v>
+        <v>3.7783</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7421</v>
+        <v>3.7783</v>
       </c>
       <c r="N18" t="n">
-        <v>141</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.7671</v>
+        <v>2.9569</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0406</v>
+        <v>1.1119</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6354</v>
+        <v>0.707</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7671</v>
+        <v>2.9569</v>
       </c>
       <c r="F19" t="n">
         <v>2.7671</v>
@@ -1320,78 +1320,78 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.7651</v>
+        <v>2.9481</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0398</v>
+        <v>1.1086</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6345</v>
+        <v>0.703</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7651</v>
+        <v>2.9481</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7651</v>
+        <v>2.9152</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.327</v>
+        <v>3.6555</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7783</v>
+        <v>4.3681</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7783</v>
+        <v>4.3681</v>
       </c>
       <c r="N20" t="n">
-        <v>207</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5372</v>
+        <v>2.6887</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9540999999999999</v>
+        <v>1.0111</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5308</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5372</v>
+        <v>2.6887</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5372</v>
+        <v>2.5051</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8283</v>
+        <v>2.758</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3796</v>
+        <v>3.2957</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3796</v>
+        <v>3.2957</v>
       </c>
       <c r="N21" t="n">
         <v>229</v>
@@ -1412,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.5307</v>
+        <v>2.5371</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9517</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5278</v>
+        <v>0.5194</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5307</v>
+        <v>2.5371</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5307</v>
+        <v>2.5371</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.814</v>
+        <v>2.8281</v>
       </c>
       <c r="I22" t="n">
-        <v>3.1957</v>
+        <v>3.3794</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1957</v>
+        <v>3.3794</v>
       </c>
       <c r="N22" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.5213</v>
+        <v>2.5204</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9478</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5235</v>
+        <v>0.512</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5213</v>
+        <v>2.5204</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5213</v>
+        <v>2.5307</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7933</v>
+        <v>2.814</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5121</v>
+        <v>3.1957</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>379</v>
+        <v>202</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5121</v>
+        <v>3.1957</v>
       </c>
       <c r="N23" t="n">
-        <v>379</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5052</v>
+        <v>2.4791</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9421</v>
+        <v>0.9323</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5162</v>
+        <v>0.4935</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5052</v>
+        <v>2.4791</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5052</v>
+        <v>2.5213</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7582</v>
+        <v>2.7933</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2959</v>
+        <v>3.5121</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>229</v>
+        <v>379</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2959</v>
+        <v>3.5121</v>
       </c>
       <c r="N24" t="n">
-        <v>229</v>
+        <v>379</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.4887</v>
+        <v>2.4424</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9359</v>
+        <v>0.9184</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5087</v>
+        <v>0.4771</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4887</v>
+        <v>2.4424</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4887</v>
+        <v>2.4885</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.722</v>
+        <v>2.7217</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2526</v>
+        <v>3.2523</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2526</v>
+        <v>3.2523</v>
       </c>
       <c r="N25" t="n">
         <v>229</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.4674</v>
+        <v>2.4392</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9172</v>
       </c>
       <c r="D26" t="n">
-        <v>0.499</v>
+        <v>0.4757</v>
       </c>
       <c r="E26" t="n">
-        <v>2.4674</v>
+        <v>2.4392</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4674</v>
+        <v>2.471</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6755</v>
+        <v>2.6834</v>
       </c>
       <c r="I26" t="n">
-        <v>3.1971</v>
+        <v>3.2065</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1971</v>
+        <v>3.2065</v>
       </c>
       <c r="N26" t="n">
         <v>229</v>
@@ -1642,507 +1642,507 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2642</v>
+        <v>2.3795</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8514</v>
+        <v>0.8948</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4065</v>
+        <v>0.4491</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2642</v>
+        <v>2.3795</v>
       </c>
       <c r="F27" t="n">
-        <v>2.2642</v>
+        <v>2.2296</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2642</v>
+        <v>2.2296</v>
       </c>
       <c r="I27" t="n">
-        <v>2.5068</v>
+        <v>2.5321</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.5068</v>
+        <v>2.5321</v>
       </c>
       <c r="N27" t="n">
-        <v>137</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.2296</v>
+        <v>2.2572</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8384</v>
+        <v>0.8488</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3908</v>
+        <v>0.3944</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2296</v>
+        <v>2.2572</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2296</v>
+        <v>2.2642</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2296</v>
+        <v>2.2642</v>
       </c>
       <c r="I28" t="n">
-        <v>2.5321</v>
+        <v>2.5068</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.5321</v>
+        <v>2.5068</v>
       </c>
       <c r="N28" t="n">
-        <v>207</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ewjerkz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.0426</v>
+        <v>2.067</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7681</v>
+        <v>0.7773</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3056</v>
+        <v>0.3095</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0426</v>
+        <v>2.067</v>
       </c>
       <c r="F29" t="n">
-        <v>2.0426</v>
+        <v>1.7948</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.0426</v>
+        <v>1.7948</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1492</v>
+        <v>1.9372</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.1492</v>
+        <v>1.9372</v>
       </c>
       <c r="N29" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>ewjerkz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.9748</v>
+        <v>2.0621</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7426</v>
+        <v>0.7754</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2748</v>
+        <v>0.3073</v>
       </c>
       <c r="E30" t="n">
-        <v>1.9748</v>
+        <v>2.0621</v>
       </c>
       <c r="F30" t="n">
-        <v>1.9748</v>
+        <v>2.0432</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.9748</v>
+        <v>2.0432</v>
       </c>
       <c r="I30" t="n">
-        <v>2.4829</v>
+        <v>2.1499</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>379</v>
+        <v>141</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.4829</v>
+        <v>2.1499</v>
       </c>
       <c r="N30" t="n">
-        <v>379</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.7948</v>
+        <v>1.9697</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.7407</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1928</v>
+        <v>0.266</v>
       </c>
       <c r="E31" t="n">
-        <v>1.7948</v>
+        <v>1.9697</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7948</v>
+        <v>1.9748</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.7948</v>
+        <v>1.9748</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9372</v>
+        <v>2.4829</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>132</v>
+        <v>379</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.9372</v>
+        <v>2.4829</v>
       </c>
       <c r="N31" t="n">
-        <v>132</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.7792</v>
+        <v>1.8142</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6691</v>
+        <v>0.6822</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1857</v>
+        <v>0.1965</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7792</v>
+        <v>1.8142</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7792</v>
+        <v>1.6407</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7792</v>
+        <v>1.6407</v>
       </c>
       <c r="I32" t="n">
-        <v>2.126</v>
+        <v>1.7708</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>246</v>
+        <v>132</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.126</v>
+        <v>1.7708</v>
       </c>
       <c r="N32" t="n">
-        <v>246</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.6963</v>
+        <v>1.7736</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6379</v>
+        <v>0.667</v>
       </c>
       <c r="D33" t="n">
-        <v>0.148</v>
+        <v>0.1784</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6963</v>
+        <v>1.7736</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6963</v>
+        <v>1.7793</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6963</v>
+        <v>1.7793</v>
       </c>
       <c r="I33" t="n">
-        <v>1.878</v>
+        <v>2.1262</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.878</v>
+        <v>2.1262</v>
       </c>
       <c r="N33" t="n">
-        <v>170</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.6558</v>
+        <v>1.6484</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6227</v>
+        <v>0.6199</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1296</v>
+        <v>0.1225</v>
       </c>
       <c r="E34" t="n">
-        <v>1.6558</v>
+        <v>1.6484</v>
       </c>
       <c r="F34" t="n">
-        <v>1.6558</v>
+        <v>1.6963</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.6558</v>
+        <v>1.6963</v>
       </c>
       <c r="I34" t="n">
-        <v>1.8804</v>
+        <v>1.878</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.8804</v>
+        <v>1.878</v>
       </c>
       <c r="N34" t="n">
-        <v>202</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.6407</v>
+        <v>1.6451</v>
       </c>
       <c r="C35" t="n">
-        <v>0.617</v>
+        <v>0.6186</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1227</v>
+        <v>0.121</v>
       </c>
       <c r="E35" t="n">
-        <v>1.6407</v>
+        <v>1.6451</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6407</v>
+        <v>1.4638</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6407</v>
+        <v>1.4638</v>
       </c>
       <c r="I35" t="n">
-        <v>1.7708</v>
+        <v>1.5015</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.7708</v>
+        <v>1.5015</v>
       </c>
       <c r="N35" t="n">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4638</v>
+        <v>1.5901</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5505</v>
+        <v>0.5979</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0421</v>
+        <v>0.0964</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4638</v>
+        <v>1.5901</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4638</v>
+        <v>1.4334</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.4638</v>
+        <v>1.4334</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5015</v>
+        <v>1.4334</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.5015</v>
+        <v>1.4334</v>
       </c>
       <c r="N36" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4334</v>
+        <v>1.4841</v>
       </c>
       <c r="C37" t="n">
-        <v>0.539</v>
+        <v>0.5581</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0283</v>
+        <v>0.0491</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4334</v>
+        <v>1.4841</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4334</v>
+        <v>1.6558</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4334</v>
+        <v>1.6558</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4334</v>
+        <v>1.8804</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4334</v>
+        <v>1.8804</v>
       </c>
       <c r="N37" t="n">
-        <v>84</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.1992</v>
+        <v>1.3054</v>
       </c>
       <c r="C38" t="n">
-        <v>0.451</v>
+        <v>0.4909</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.0307</v>
       </c>
       <c r="E38" t="n">
-        <v>1.1992</v>
+        <v>1.3054</v>
       </c>
       <c r="F38" t="n">
         <v>1.1992</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.1723</v>
+        <v>1.1066</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4408</v>
+        <v>0.4161</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0905</v>
+        <v>-0.1195</v>
       </c>
       <c r="E39" t="n">
-        <v>1.1723</v>
+        <v>1.1066</v>
       </c>
       <c r="F39" t="n">
         <v>1.1723</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.1314</v>
+        <v>0.9366</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4255</v>
+        <v>0.3522</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1092</v>
+        <v>-0.1955</v>
       </c>
       <c r="E40" t="n">
-        <v>1.1314</v>
+        <v>0.9366</v>
       </c>
       <c r="F40" t="n">
         <v>1.1314</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9937</v>
+        <v>0.8147</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3737</v>
+        <v>0.3064</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1719</v>
+        <v>-0.2499</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9937</v>
+        <v>0.8147</v>
       </c>
       <c r="F41" t="n">
         <v>0.9937</v>
@@ -2332,47 +2332,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sirah</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.948</v>
+        <v>0.7938</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3565</v>
+        <v>0.2985</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1927</v>
+        <v>-0.2592</v>
       </c>
       <c r="E42" t="n">
-        <v>0.948</v>
+        <v>0.7938</v>
       </c>
       <c r="F42" t="n">
-        <v>0.948</v>
+        <v>0.856</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.948</v>
+        <v>0.856</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0496</v>
+        <v>1.0763</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>170</v>
+        <v>379</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.0496</v>
+        <v>1.0763</v>
       </c>
       <c r="N42" t="n">
-        <v>170</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9231</v>
+        <v>0.779</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3471</v>
+        <v>0.2929</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.204</v>
+        <v>-0.2659</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9231</v>
+        <v>0.779</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9231</v>
+        <v>0.9149</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9231</v>
+        <v>0.9149</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9627</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9627</v>
       </c>
       <c r="N43" t="n">
         <v>141</v>
@@ -2424,47 +2424,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>sirah</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.856</v>
+        <v>0.7594</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3219</v>
+        <v>0.2856</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2345</v>
+        <v>-0.2746</v>
       </c>
       <c r="E44" t="n">
-        <v>0.856</v>
+        <v>0.7594</v>
       </c>
       <c r="F44" t="n">
-        <v>0.856</v>
+        <v>0.948</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.856</v>
+        <v>0.948</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0763</v>
+        <v>1.0496</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>379</v>
+        <v>170</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.0763</v>
+        <v>1.0496</v>
       </c>
       <c r="N44" t="n">
-        <v>379</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45">
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7861</v>
+        <v>0.6667</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2956</v>
+        <v>0.2507</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2664</v>
+        <v>-0.316</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7861</v>
+        <v>0.6667</v>
       </c>
       <c r="F45" t="n">
         <v>0.7861</v>
@@ -2516,93 +2516,93 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.652</v>
+        <v>0.6005</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2452</v>
+        <v>0.2258</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3274</v>
+        <v>-0.3456</v>
       </c>
       <c r="E46" t="n">
-        <v>0.652</v>
+        <v>0.6005</v>
       </c>
       <c r="F46" t="n">
-        <v>0.652</v>
+        <v>0.4959</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.652</v>
+        <v>0.4959</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7218</v>
+        <v>0.5087</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>197</v>
+        <v>109</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7218</v>
+        <v>0.5087</v>
       </c>
       <c r="N46" t="n">
-        <v>197</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6091</v>
+        <v>0.5743</v>
       </c>
       <c r="C47" t="n">
-        <v>0.229</v>
+        <v>0.216</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3469</v>
+        <v>-0.3573</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6091</v>
+        <v>0.5743</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6091</v>
+        <v>0.652</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6091</v>
+        <v>0.652</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7278</v>
+        <v>0.7218</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7278</v>
+        <v>0.7218</v>
       </c>
       <c r="N47" t="n">
-        <v>229</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48">
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5471</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2057</v>
+        <v>0.214</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3752</v>
+        <v>-0.3596</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5471</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5471</v>
+        <v>0.5393</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5471</v>
+        <v>0.5393</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5757</v>
+        <v>0.5674</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5757</v>
+        <v>0.5674</v>
       </c>
       <c r="N48" t="n">
         <v>141</v>
@@ -2654,323 +2654,323 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4959</v>
+        <v>0.5622</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1865</v>
+        <v>0.2114</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3985</v>
+        <v>-0.3627</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4959</v>
+        <v>0.5622</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4959</v>
+        <v>0.6089</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4959</v>
+        <v>0.6089</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5087</v>
+        <v>0.7276</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5087</v>
+        <v>0.7276</v>
       </c>
       <c r="N49" t="n">
-        <v>109</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3347</v>
+        <v>0.2835</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1259</v>
+        <v>0.1066</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4718</v>
+        <v>-0.4872</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3347</v>
+        <v>0.2835</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3347</v>
+        <v>0.1532</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3347</v>
+        <v>0.1532</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3613</v>
+        <v>0.1653</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.3613</v>
+        <v>0.1653</v>
       </c>
       <c r="N50" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1532</v>
+        <v>0.2436</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0576</v>
+        <v>0.0916</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5545</v>
+        <v>-0.505</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1532</v>
+        <v>0.2436</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1532</v>
+        <v>0.3347</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1532</v>
+        <v>0.3347</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1653</v>
+        <v>0.3613</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1653</v>
+        <v>0.3613</v>
       </c>
       <c r="N51" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ArtFr0st</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.1175</v>
+        <v>0.0105</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0442</v>
+        <v>0.0039</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5707</v>
+        <v>-0.6091</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1175</v>
+        <v>0.0105</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1175</v>
+        <v>-0.0004</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1175</v>
+        <v>-0.0004</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1301</v>
+        <v>-0.0004</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1301</v>
+        <v>-0.0004</v>
       </c>
       <c r="N52" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0844</v>
+        <v>-0.0516</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0317</v>
+        <v>-0.0194</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5858</v>
+        <v>-0.6369</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0844</v>
+        <v>-0.0516</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0844</v>
+        <v>0.013</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0844</v>
+        <v>0.013</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1009</v>
+        <v>0.014</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>246</v>
+        <v>140</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1009</v>
+        <v>0.014</v>
       </c>
       <c r="N53" t="n">
-        <v>246</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>d4rty</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.013</v>
+        <v>-0.0579</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0049</v>
+        <v>-0.0218</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6183</v>
+        <v>-0.6397</v>
       </c>
       <c r="E54" t="n">
-        <v>0.013</v>
+        <v>-0.0579</v>
       </c>
       <c r="F54" t="n">
-        <v>0.013</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.013</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>0.014</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.014</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>140</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0004</v>
+        <v>-0.0741</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0002</v>
+        <v>-0.0279</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6244</v>
+        <v>-0.6469</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0004</v>
+        <v>-0.0741</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0004</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0004</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0004</v>
+        <v>0.0877</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>109</v>
+        <v>246</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0004</v>
+        <v>0.0877</v>
       </c>
       <c r="N55" t="n">
-        <v>109</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56">
@@ -2980,16 +2980,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0062</v>
+        <v>-0.0788</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0023</v>
+        <v>-0.0296</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.627</v>
+        <v>-0.649</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0062</v>
+        <v>-0.0788</v>
       </c>
       <c r="F56" t="n">
         <v>-0.0062</v>
@@ -3022,78 +3022,78 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>ArtFr0st</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.049</v>
+        <v>-0.1267</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0184</v>
+        <v>-0.0476</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6465</v>
+        <v>-0.6704</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.049</v>
+        <v>-0.1267</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.049</v>
+        <v>0.1175</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.049</v>
+        <v>0.1175</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0529</v>
+        <v>0.1301</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.0529</v>
+        <v>0.1301</v>
       </c>
       <c r="N57" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>d4rty</t>
+          <t>Cryptic</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.0553</v>
+        <v>-0.175</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0208</v>
+        <v>-0.0658</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6494</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.0553</v>
+        <v>-0.175</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.0553</v>
+        <v>-0.1807</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.0553</v>
+        <v>-0.1807</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0567</v>
+        <v>-0.1854</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.0567</v>
+        <v>-0.1854</v>
       </c>
       <c r="N58" t="n">
         <v>92</v>
@@ -3114,78 +3114,78 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.0823</v>
+        <v>-0.2015</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0309</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6617</v>
+        <v>-0.7038</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0823</v>
+        <v>-0.2015</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0823</v>
+        <v>-0.049</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.0823</v>
+        <v>-0.049</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0844</v>
+        <v>-0.0529</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.0844</v>
+        <v>-0.0529</v>
       </c>
       <c r="N59" t="n">
-        <v>109</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>maNkz</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.1059</v>
+        <v>-0.3078</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0398</v>
+        <v>-0.1157</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6724</v>
+        <v>-0.7513</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.1059</v>
+        <v>-0.3078</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1059</v>
+        <v>-0.4328</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1059</v>
+        <v>-0.4328</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1059</v>
+        <v>-0.4328</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.1059</v>
+        <v>-0.4328</v>
       </c>
       <c r="N60" t="n">
         <v>84</v>
@@ -3206,185 +3206,185 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.174</v>
+        <v>-0.3514</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0654</v>
+        <v>-0.1321</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7034</v>
+        <v>-0.7708</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.174</v>
+        <v>-0.3514</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.174</v>
+        <v>-0.3778</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.174</v>
+        <v>-0.3778</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2244</v>
+        <v>-0.3778</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.2244</v>
+        <v>-0.3778</v>
       </c>
       <c r="N61" t="n">
-        <v>258</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cryptic</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.1799</v>
+        <v>-0.3928</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0677</v>
+        <v>-0.1477</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7893</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1799</v>
+        <v>-0.3928</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1799</v>
+        <v>-0.1059</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.1799</v>
+        <v>-0.1059</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1845</v>
+        <v>-0.1059</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.1845</v>
+        <v>-0.1059</v>
       </c>
       <c r="N62" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3778</v>
+        <v>-0.4334</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1421</v>
+        <v>-0.163</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7962</v>
+        <v>-0.8074</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3778</v>
+        <v>-0.4334</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3778</v>
+        <v>-0.0823</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3778</v>
+        <v>-0.0823</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3778</v>
+        <v>-0.0844</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3778</v>
+        <v>-0.0844</v>
       </c>
       <c r="N63" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3805</v>
+        <v>-0.4794</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1431</v>
+        <v>-0.1803</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7974</v>
+        <v>-0.828</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3805</v>
+        <v>-0.4794</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3805</v>
+        <v>-0.174</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.3805</v>
+        <v>-0.174</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4213</v>
+        <v>-0.2244</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4213</v>
+        <v>-0.2244</v>
       </c>
       <c r="N64" t="n">
-        <v>197</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65">
@@ -3394,16 +3394,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3999</v>
+        <v>-0.5797</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1504</v>
+        <v>-0.218</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8062</v>
+        <v>-0.8728</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3999</v>
+        <v>-0.5797</v>
       </c>
       <c r="F65" t="n">
         <v>-0.3999</v>
@@ -3436,93 +3436,93 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>maNkz</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4328</v>
+        <v>-0.5996</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1628</v>
+        <v>-0.2255</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8212</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4328</v>
+        <v>-0.5996</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4328</v>
+        <v>-0.3805</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4328</v>
+        <v>-0.3805</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4328</v>
+        <v>-0.4213</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4328</v>
+        <v>-0.4213</v>
       </c>
       <c r="N66" t="n">
-        <v>84</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>arrozdoce</t>
+          <t>SLIGHT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.6118</v>
+        <v>-0.6429</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2301</v>
+        <v>-0.2418</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.901</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.6118</v>
+        <v>-0.6429</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.6118</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.6118</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.6437</v>
+        <v>-0.8464</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.6437</v>
+        <v>-0.8464</v>
       </c>
       <c r="N67" t="n">
-        <v>141</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68">
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7415</v>
+        <v>-0.6792</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2788</v>
+        <v>-0.2554</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9617</v>
+        <v>-0.9172</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7415</v>
+        <v>-0.6792</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.7415</v>
+        <v>-0.7423</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7415</v>
+        <v>-0.7423</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.7614</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.7614</v>
       </c>
       <c r="N68" t="n">
         <v>92</v>
@@ -3574,185 +3574,185 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>brett</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7619</v>
+        <v>-0.729</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2865</v>
+        <v>-0.2741</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.971</v>
+        <v>-0.9394</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7619</v>
+        <v>-0.729</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7619</v>
+        <v>-0.8999</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7619</v>
+        <v>-0.8999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7815</v>
+        <v>-0.9231</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.7815</v>
+        <v>-0.9231</v>
       </c>
       <c r="N69" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>arrozdoce</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.7664</v>
+        <v>-0.8242</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2882</v>
+        <v>-0.3099</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9731</v>
+        <v>-0.982</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.7664</v>
+        <v>-0.8242</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.7664</v>
+        <v>-0.6099</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.7664</v>
+        <v>-0.6099</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8704</v>
+        <v>-0.6417</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8704</v>
+        <v>-0.6417</v>
       </c>
       <c r="N70" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SLIGHT</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8246</v>
+        <v>-0.8874</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3101</v>
+        <v>-0.3337</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9996</v>
+        <v>-1.0102</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8246</v>
+        <v>-0.8874</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8246</v>
+        <v>-0.7664</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.8246</v>
+        <v>-0.7664</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8458</v>
+        <v>-0.8704</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>92</v>
+        <v>202</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8458</v>
+        <v>-0.8704</v>
       </c>
       <c r="N71" t="n">
-        <v>92</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>brett</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.8999</v>
+        <v>-0.9015</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3384</v>
+        <v>-0.339</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0339</v>
+        <v>-1.0165</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.8999</v>
+        <v>-0.9015</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.8999</v>
+        <v>-0.7619</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.8999</v>
+        <v>-0.7619</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9231</v>
+        <v>-0.7815</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9231</v>
+        <v>-0.7815</v>
       </c>
       <c r="N72" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73">
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9563</v>
+        <v>-1.1476</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.3596</v>
+        <v>-0.4315</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0595</v>
+        <v>-1.1264</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9563</v>
+        <v>-1.1476</v>
       </c>
       <c r="F73" t="n">
         <v>-0.9563</v>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.9806</v>
+        <v>-1.196</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.3687</v>
+        <v>-0.4497</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0706</v>
+        <v>-1.148</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.9806</v>
+        <v>-1.196</v>
       </c>
       <c r="F74" t="n">
         <v>-0.9806</v>
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1555</v>
+        <v>-1.364</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4345</v>
+        <v>-0.5129</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1502</v>
+        <v>-1.2231</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1555</v>
+        <v>-1.364</v>
       </c>
       <c r="F75" t="n">
         <v>-1.1555</v>
@@ -3900,16 +3900,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.1878</v>
+        <v>-1.4878</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.4467</v>
+        <v>-0.5595</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1649</v>
+        <v>-1.2784</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.1878</v>
+        <v>-1.4878</v>
       </c>
       <c r="F76" t="n">
         <v>-1.1878</v>
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3684</v>
+        <v>-1.5089</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.5674</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2471</v>
+        <v>-1.2878</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3684</v>
+        <v>-1.5089</v>
       </c>
       <c r="F77" t="n">
         <v>-1.3684</v>
@@ -3988,93 +3988,93 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WolfY</t>
+          <t>cJ dA K1nG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.4961</v>
+        <v>-1.6492</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5626</v>
+        <v>-0.6202</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3053</v>
+        <v>-1.3505</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.4961</v>
+        <v>-1.6492</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.4961</v>
+        <v>-1.6062</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.4961</v>
+        <v>-1.6062</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.4961</v>
+        <v>-1.6476</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.4961</v>
+        <v>-1.6476</v>
       </c>
       <c r="N78" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>cJ dA K1nG</t>
+          <t>WolfY</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.6062</v>
+        <v>-1.9562</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.604</v>
+        <v>-0.7356</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3554</v>
+        <v>-1.4876</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.6062</v>
+        <v>-1.9562</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.6062</v>
+        <v>-1.4961</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.6062</v>
+        <v>-1.4961</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.6476</v>
+        <v>-1.4961</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.6476</v>
+        <v>-1.4961</v>
       </c>
       <c r="N79" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80">
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.849</v>
+        <v>-2.192</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.6953</v>
+        <v>-0.8243</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4659</v>
+        <v>-1.5929</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.849</v>
+        <v>-2.192</v>
       </c>
       <c r="F80" t="n">
         <v>-1.849</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.0538</v>
+        <v>-3.3611</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.1484</v>
+        <v>-1.2639</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0144</v>
+        <v>-2.1152</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.0538</v>
+        <v>-3.3611</v>
       </c>
       <c r="F81" t="n">
         <v>-3.0538</v>
@@ -5069,10 +5069,10 @@
         <v>1.72</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8368</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>15.8992</v>
+        <v>15.9068</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.38</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4966</v>
+        <v>0.4969</v>
       </c>
       <c r="J23" t="n">
-        <v>9.4354</v>
+        <v>9.4411</v>
       </c>
     </row>
     <row r="24">
@@ -5146,13 +5146,13 @@
         <v>19</v>
       </c>
       <c r="H24" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2226</v>
+        <v>0.2094</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2294</v>
+        <v>3.9786</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0902</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7157</v>
+        <v>-1.7138</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1172</v>
+        <v>-0.117</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.2268</v>
+        <v>-2.223</v>
       </c>
     </row>
     <row r="27">
@@ -6269,10 +6269,10 @@
         <v>1.69</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7895</v>
       </c>
       <c r="J52" t="n">
-        <v>15.796</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.58</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6851</v>
+        <v>0.6849</v>
       </c>
       <c r="J53" t="n">
-        <v>13.702</v>
+        <v>13.698</v>
       </c>
     </row>
     <row r="54">
@@ -6346,13 +6346,13 @@
         <v>20</v>
       </c>
       <c r="H54" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6561</v>
+        <v>0.6655</v>
       </c>
       <c r="J54" t="n">
-        <v>13.122</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.08</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1286</v>
+        <v>0.1284</v>
       </c>
       <c r="J55" t="n">
-        <v>2.572</v>
+        <v>2.568</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.78</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2971</v>
+        <v>-0.2973</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.942</v>
+        <v>-5.946</v>
       </c>
     </row>
     <row r="57">
@@ -23466,13 +23466,13 @@
         <v>22</v>
       </c>
       <c r="H482" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="I482" t="n">
-        <v>0.6931</v>
+        <v>0.7408</v>
       </c>
       <c r="J482" t="n">
-        <v>15.2482</v>
+        <v>16.2976</v>
       </c>
     </row>
     <row r="483">
@@ -23509,10 +23509,10 @@
         <v>1.18</v>
       </c>
       <c r="I483" t="n">
-        <v>0.2775</v>
+        <v>0.2767</v>
       </c>
       <c r="J483" t="n">
-        <v>6.105</v>
+        <v>6.0874</v>
       </c>
     </row>
     <row r="484">
@@ -23549,10 +23549,10 @@
         <v>1.16</v>
       </c>
       <c r="I484" t="n">
-        <v>0.2531</v>
+        <v>0.2525</v>
       </c>
       <c r="J484" t="n">
-        <v>5.5682</v>
+        <v>5.555</v>
       </c>
     </row>
     <row r="485">
@@ -23586,13 +23586,13 @@
         <v>22</v>
       </c>
       <c r="H485" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I485" t="n">
-        <v>-0.0706</v>
+        <v>-0.0558</v>
       </c>
       <c r="J485" t="n">
-        <v>-1.5532</v>
+        <v>-1.2276</v>
       </c>
     </row>
     <row r="486">
@@ -23629,10 +23629,10 @@
         <v>0.93</v>
       </c>
       <c r="I486" t="n">
-        <v>-0.1246</v>
+        <v>-0.1255</v>
       </c>
       <c r="J486" t="n">
-        <v>-2.7412</v>
+        <v>-2.761</v>
       </c>
     </row>
     <row r="487">
@@ -23666,13 +23666,13 @@
         <v>22</v>
       </c>
       <c r="H487" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="I487" t="n">
-        <v>0.4619</v>
+        <v>0.4382</v>
       </c>
       <c r="J487" t="n">
-        <v>10.1618</v>
+        <v>9.6404</v>
       </c>
     </row>
     <row r="488">
@@ -23709,10 +23709,10 @@
         <v>1.21</v>
       </c>
       <c r="I488" t="n">
-        <v>0.3698</v>
+        <v>0.3718</v>
       </c>
       <c r="J488" t="n">
-        <v>8.1356</v>
+        <v>8.179600000000001</v>
       </c>
     </row>
     <row r="489">
@@ -23749,10 +23749,10 @@
         <v>0.74</v>
       </c>
       <c r="I489" t="n">
-        <v>-0.303</v>
+        <v>-0.3023</v>
       </c>
       <c r="J489" t="n">
-        <v>-6.666</v>
+        <v>-6.6506</v>
       </c>
     </row>
     <row r="490">
@@ -23786,13 +23786,13 @@
         <v>22</v>
       </c>
       <c r="H490" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="I490" t="n">
-        <v>-0.3218</v>
+        <v>-0.3304</v>
       </c>
       <c r="J490" t="n">
-        <v>-7.0796</v>
+        <v>-7.2688</v>
       </c>
     </row>
     <row r="491">
@@ -23826,13 +23826,13 @@
         <v>22</v>
       </c>
       <c r="H491" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I491" t="n">
-        <v>-0.3769</v>
+        <v>-0.3852</v>
       </c>
       <c r="J491" t="n">
-        <v>-8.2918</v>
+        <v>-8.474399999999999</v>
       </c>
     </row>
     <row r="492">
